--- a/data/Bacterie_sensibilite.xlsx
+++ b/data/Bacterie_sensibilite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\Documents\Projet\smart-vap-python\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rthouv/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5624586-16A8-4345-8F1C-1636C002AEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0063107A-4C55-2246-A0DC-FFEEAD186A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="106">
   <si>
     <t xml:space="preserve">Antibiotique efficace </t>
   </si>
@@ -317,13 +317,7 @@
     <t>type</t>
   </si>
   <si>
-    <t>Imipenem+ Gentamicine</t>
-  </si>
-  <si>
     <t>Imipenem+ Amikacine</t>
-  </si>
-  <si>
-    <t>Cefepime+Gentamicine</t>
   </si>
   <si>
     <t>Ceftriaxone ou Cefotaxime</t>
@@ -334,12 +328,35 @@
   <si>
     <t>OXA-48-like</t>
   </si>
+  <si>
+    <t>Meropenem</t>
+  </si>
+  <si>
+    <t>Cefepime</t>
+  </si>
+  <si>
+    <t>"Cefepime + Amikacine 
+sauf Si Infection récente à  P. aeruginosa &lt; 1 mois
+-Pas d'exposition aux carbapenemes &lt; 1 mois : Meropenem + Amikacine
+- Exposition aux carbapenemes &lt; 1 mois : Ceftolozane/Tazobactam + Amikacine "</t>
+  </si>
+  <si>
+    <t>MecA</t>
+  </si>
+  <si>
+    <t>Cefepime/enmetazobactam
+ou
+Ceftazidime/avibactam</t>
+  </si>
+  <si>
+    <t>Aztreonam/avibactam</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -349,23 +366,34 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -382,6 +410,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -395,6 +424,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -861,110 +891,110 @@
   </cellStyleXfs>
   <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1183,19 +1213,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.3984375" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
     <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="14.296875" customWidth="1"/>
-    <col min="6" max="6" width="5.796875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="5.83203125" customWidth="1"/>
     <col min="7" max="18" width="6" customWidth="1"/>
-    <col min="19" max="37" width="10.59765625" customWidth="1"/>
+    <col min="19" max="37" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15.75" customHeight="1">
+    <row r="1" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1234,7 +1264,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" ht="15.75" customHeight="1">
+    <row r="2" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1275,7 +1305,7 @@
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
     </row>
-    <row r="3" spans="1:37" ht="210" customHeight="1">
+    <row r="3" spans="1:37" ht="210" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>1</v>
@@ -1343,7 +1373,7 @@
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
     </row>
-    <row r="4" spans="1:37" ht="15.75" customHeight="1">
+    <row r="4" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -1389,7 +1419,7 @@
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
     </row>
-    <row r="5" spans="1:37" ht="15.75" customHeight="1">
+    <row r="5" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="8"/>
@@ -1429,7 +1459,7 @@
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
     </row>
-    <row r="6" spans="1:37" ht="15.75" customHeight="1">
+    <row r="6" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="12"/>
@@ -1469,7 +1499,7 @@
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
     </row>
-    <row r="7" spans="1:37" ht="15.75" customHeight="1">
+    <row r="7" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="14" t="s">
@@ -1515,7 +1545,7 @@
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
     </row>
-    <row r="8" spans="1:37" ht="15.75" customHeight="1">
+    <row r="8" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="14" t="s">
@@ -1563,7 +1593,7 @@
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
     </row>
-    <row r="9" spans="1:37" ht="15.75" customHeight="1">
+    <row r="9" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="14" t="s">
@@ -1613,7 +1643,7 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:37" ht="15.75" customHeight="1">
+    <row r="10" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="14" t="s">
@@ -1667,7 +1697,7 @@
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
     </row>
-    <row r="11" spans="1:37" ht="15.75" customHeight="1">
+    <row r="11" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="1"/>
       <c r="C11" s="17" t="s">
@@ -1711,7 +1741,7 @@
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
     </row>
-    <row r="12" spans="1:37" ht="15.75" customHeight="1">
+    <row r="12" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -1775,7 +1805,7 @@
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
     </row>
-    <row r="13" spans="1:37" ht="15.75" customHeight="1">
+    <row r="13" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="17"/>
       <c r="C13" s="14" t="s">
@@ -1827,7 +1857,7 @@
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
     </row>
-    <row r="14" spans="1:37" ht="15.75" customHeight="1">
+    <row r="14" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="17"/>
       <c r="C14" s="4" t="s">
@@ -1887,7 +1917,7 @@
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
     </row>
-    <row r="15" spans="1:37" ht="15.75" customHeight="1">
+    <row r="15" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="17"/>
       <c r="C15" s="22"/>
@@ -1929,7 +1959,7 @@
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
     </row>
-    <row r="16" spans="1:37" ht="15.75" customHeight="1">
+    <row r="16" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="17"/>
       <c r="C16" s="4" t="s">
@@ -1991,7 +2021,7 @@
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
     </row>
-    <row r="17" spans="1:37" ht="15.75" customHeight="1">
+    <row r="17" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -2033,7 +2063,7 @@
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
     </row>
-    <row r="18" spans="1:37" ht="15.75" customHeight="1">
+    <row r="18" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -2075,7 +2105,7 @@
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
     </row>
-    <row r="19" spans="1:37" ht="15.75" customHeight="1">
+    <row r="19" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -2117,7 +2147,7 @@
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
     </row>
-    <row r="20" spans="1:37" ht="15.75" customHeight="1">
+    <row r="20" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="28"/>
       <c r="C20" s="12"/>
@@ -2159,7 +2189,7 @@
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
     </row>
-    <row r="21" spans="1:37" ht="15.75" customHeight="1">
+    <row r="21" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="17"/>
       <c r="C21" s="12" t="s">
@@ -2215,7 +2245,7 @@
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
     </row>
-    <row r="22" spans="1:37" ht="15.75" customHeight="1">
+    <row r="22" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="31"/>
       <c r="C22" s="29" t="s">
@@ -2267,7 +2297,7 @@
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
     </row>
-    <row r="23" spans="1:37" ht="15.75" customHeight="1">
+    <row r="23" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="12" t="s">
@@ -2333,7 +2363,7 @@
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
     </row>
-    <row r="24" spans="1:37" ht="15.75" customHeight="1">
+    <row r="24" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
       <c r="C24" s="4" t="s">
@@ -2397,7 +2427,7 @@
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
     </row>
-    <row r="25" spans="1:37" ht="15.75" customHeight="1">
+    <row r="25" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2"/>
       <c r="C25" s="17"/>
@@ -2439,7 +2469,7 @@
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
     </row>
-    <row r="26" spans="1:37" ht="15.75" customHeight="1">
+    <row r="26" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
       <c r="C26" s="17"/>
@@ -2481,7 +2511,7 @@
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
     </row>
-    <row r="27" spans="1:37" ht="15.75" customHeight="1">
+    <row r="27" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
       <c r="C27" s="4"/>
@@ -2541,7 +2571,7 @@
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
     </row>
-    <row r="28" spans="1:37" ht="15.75" customHeight="1">
+    <row r="28" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2"/>
       <c r="C28" s="4" t="s">
@@ -2587,7 +2617,7 @@
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
     </row>
-    <row r="29" spans="1:37" ht="15.75" customHeight="1">
+    <row r="29" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2"/>
       <c r="C29" s="17"/>
@@ -2629,7 +2659,7 @@
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
     </row>
-    <row r="30" spans="1:37" ht="15.75" customHeight="1">
+    <row r="30" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2"/>
       <c r="C30" s="12"/>
@@ -2671,7 +2701,7 @@
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
     </row>
-    <row r="31" spans="1:37" ht="15.75" customHeight="1">
+    <row r="31" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="36" t="s">
         <v>75</v>
@@ -2715,7 +2745,7 @@
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
     </row>
-    <row r="32" spans="1:37" ht="15.75" customHeight="1">
+    <row r="32" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2746,7 +2776,7 @@
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
     </row>
-    <row r="33" spans="1:37" ht="15.75" customHeight="1">
+    <row r="33" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2777,7 +2807,7 @@
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
     </row>
-    <row r="34" spans="1:37" ht="15.75" customHeight="1">
+    <row r="34" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2818,7 +2848,7 @@
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
     </row>
-    <row r="35" spans="1:37" ht="15.75" customHeight="1">
+    <row r="35" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2859,7 +2889,7 @@
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
     </row>
-    <row r="36" spans="1:37" ht="15.75" customHeight="1">
+    <row r="36" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2904,7 +2934,7 @@
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
     </row>
-    <row r="37" spans="1:37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2943,7 +2973,7 @@
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
     </row>
-    <row r="38" spans="1:37" ht="15.75" customHeight="1">
+    <row r="38" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="2"/>
@@ -2982,7 +3012,7 @@
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
     </row>
-    <row r="39" spans="1:37" ht="15.75" customHeight="1">
+    <row r="39" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="2"/>
@@ -3021,7 +3051,7 @@
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
     </row>
-    <row r="40" spans="1:37" ht="15.75" customHeight="1">
+    <row r="40" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -3060,7 +3090,7 @@
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
     </row>
-    <row r="41" spans="1:37" ht="15.75" customHeight="1">
+    <row r="41" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -3099,7 +3129,7 @@
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
     </row>
-    <row r="42" spans="1:37" ht="15.75" customHeight="1">
+    <row r="42" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="2"/>
@@ -3138,7 +3168,7 @@
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
     </row>
-    <row r="43" spans="1:37" ht="15.75" customHeight="1">
+    <row r="43" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="2"/>
@@ -3177,7 +3207,7 @@
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
     </row>
-    <row r="44" spans="1:37" ht="15.75" customHeight="1">
+    <row r="44" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -3216,7 +3246,7 @@
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
     </row>
-    <row r="45" spans="1:37" ht="15.75" customHeight="1">
+    <row r="45" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="2"/>
@@ -3255,7 +3285,7 @@
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
     </row>
-    <row r="46" spans="1:37" ht="15.75" customHeight="1">
+    <row r="46" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="2"/>
@@ -3294,7 +3324,7 @@
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
     </row>
-    <row r="47" spans="1:37" ht="15.75" customHeight="1">
+    <row r="47" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3333,7 +3363,7 @@
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
     </row>
-    <row r="48" spans="1:37" ht="15.75" customHeight="1">
+    <row r="48" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="2"/>
@@ -3372,7 +3402,7 @@
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
     </row>
-    <row r="49" spans="1:37" ht="15.75" customHeight="1">
+    <row r="49" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="2"/>
@@ -3411,7 +3441,7 @@
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
     </row>
-    <row r="50" spans="1:37" ht="15.75" customHeight="1">
+    <row r="50" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -3450,7 +3480,7 @@
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
     </row>
-    <row r="51" spans="1:37" ht="15.75" customHeight="1">
+    <row r="51" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="2"/>
@@ -3489,7 +3519,7 @@
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
     </row>
-    <row r="52" spans="1:37" ht="15.75" customHeight="1">
+    <row r="52" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="2"/>
@@ -3528,7 +3558,7 @@
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
     </row>
-    <row r="53" spans="1:37" ht="15.75" customHeight="1">
+    <row r="53" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -3567,7 +3597,7 @@
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
     </row>
-    <row r="54" spans="1:37" ht="15.75" customHeight="1">
+    <row r="54" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="2"/>
@@ -3606,7 +3636,7 @@
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
     </row>
-    <row r="55" spans="1:37" ht="15.75" customHeight="1">
+    <row r="55" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="2"/>
@@ -3645,7 +3675,7 @@
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
     </row>
-    <row r="56" spans="1:37" ht="15.75" customHeight="1">
+    <row r="56" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -3684,7 +3714,7 @@
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
     </row>
-    <row r="57" spans="1:37" ht="15.75" customHeight="1">
+    <row r="57" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3723,7 +3753,7 @@
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
     </row>
-    <row r="58" spans="1:37" ht="15.75" customHeight="1">
+    <row r="58" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3762,7 +3792,7 @@
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
     </row>
-    <row r="59" spans="1:37" ht="15.75" customHeight="1">
+    <row r="59" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3801,7 +3831,7 @@
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
     </row>
-    <row r="60" spans="1:37" ht="15.75" customHeight="1">
+    <row r="60" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3840,7 +3870,7 @@
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
     </row>
-    <row r="61" spans="1:37" ht="15.75" customHeight="1">
+    <row r="61" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3879,7 +3909,7 @@
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
     </row>
-    <row r="62" spans="1:37" ht="15.75" customHeight="1">
+    <row r="62" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3918,7 +3948,7 @@
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
     </row>
-    <row r="63" spans="1:37" ht="15.75" customHeight="1">
+    <row r="63" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3957,7 +3987,7 @@
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
     </row>
-    <row r="64" spans="1:37" ht="15.75" customHeight="1">
+    <row r="64" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3996,7 +4026,7 @@
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
     </row>
-    <row r="65" spans="1:37" ht="15.75" customHeight="1">
+    <row r="65" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -4035,7 +4065,7 @@
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
     </row>
-    <row r="66" spans="1:37" ht="15.75" customHeight="1">
+    <row r="66" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -4074,7 +4104,7 @@
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
     </row>
-    <row r="67" spans="1:37" ht="15.75" customHeight="1">
+    <row r="67" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -4113,7 +4143,7 @@
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
     </row>
-    <row r="68" spans="1:37" ht="15.75" customHeight="1">
+    <row r="68" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -4152,7 +4182,7 @@
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
     </row>
-    <row r="69" spans="1:37" ht="15.75" customHeight="1">
+    <row r="69" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -4191,7 +4221,7 @@
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
     </row>
-    <row r="70" spans="1:37" ht="15.75" customHeight="1">
+    <row r="70" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -4230,7 +4260,7 @@
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
     </row>
-    <row r="71" spans="1:37" ht="15.75" customHeight="1">
+    <row r="71" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -4269,7 +4299,7 @@
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
     </row>
-    <row r="72" spans="1:37" ht="15.75" customHeight="1">
+    <row r="72" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -4308,7 +4338,7 @@
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
     </row>
-    <row r="73" spans="1:37" ht="15.75" customHeight="1">
+    <row r="73" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -4347,7 +4377,7 @@
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
     </row>
-    <row r="74" spans="1:37" ht="15.75" customHeight="1">
+    <row r="74" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -4386,7 +4416,7 @@
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
     </row>
-    <row r="75" spans="1:37" ht="15.75" customHeight="1">
+    <row r="75" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -4425,7 +4455,7 @@
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
     </row>
-    <row r="76" spans="1:37" ht="15.75" customHeight="1">
+    <row r="76" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -4464,7 +4494,7 @@
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
     </row>
-    <row r="77" spans="1:37" ht="15.75" customHeight="1">
+    <row r="77" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -4503,7 +4533,7 @@
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
     </row>
-    <row r="78" spans="1:37" ht="15.75" customHeight="1">
+    <row r="78" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -4542,7 +4572,7 @@
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
     </row>
-    <row r="79" spans="1:37" ht="15.75" customHeight="1">
+    <row r="79" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -4581,7 +4611,7 @@
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
     </row>
-    <row r="80" spans="1:37" ht="15.75" customHeight="1">
+    <row r="80" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -4620,7 +4650,7 @@
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
     </row>
-    <row r="81" spans="1:37" ht="15.75" customHeight="1">
+    <row r="81" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -4659,7 +4689,7 @@
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
     </row>
-    <row r="82" spans="1:37" ht="15.75" customHeight="1">
+    <row r="82" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -4698,7 +4728,7 @@
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
     </row>
-    <row r="83" spans="1:37" ht="15.75" customHeight="1">
+    <row r="83" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4737,7 +4767,7 @@
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
     </row>
-    <row r="84" spans="1:37" ht="15.75" customHeight="1">
+    <row r="84" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -4776,7 +4806,7 @@
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
     </row>
-    <row r="85" spans="1:37" ht="15.75" customHeight="1">
+    <row r="85" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4815,7 +4845,7 @@
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
     </row>
-    <row r="86" spans="1:37" ht="15.75" customHeight="1">
+    <row r="86" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4854,7 +4884,7 @@
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
     </row>
-    <row r="87" spans="1:37" ht="15.75" customHeight="1">
+    <row r="87" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4893,7 +4923,7 @@
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
     </row>
-    <row r="88" spans="1:37" ht="15.75" customHeight="1">
+    <row r="88" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -4932,7 +4962,7 @@
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
     </row>
-    <row r="89" spans="1:37" ht="15.75" customHeight="1">
+    <row r="89" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4971,7 +5001,7 @@
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
     </row>
-    <row r="90" spans="1:37" ht="15.75" customHeight="1">
+    <row r="90" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -5010,7 +5040,7 @@
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
     </row>
-    <row r="91" spans="1:37" ht="15.75" customHeight="1">
+    <row r="91" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -5049,7 +5079,7 @@
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
     </row>
-    <row r="92" spans="1:37" ht="15.75" customHeight="1">
+    <row r="92" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -5088,7 +5118,7 @@
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
     </row>
-    <row r="93" spans="1:37" ht="15.75" customHeight="1">
+    <row r="93" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -5127,7 +5157,7 @@
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
     </row>
-    <row r="94" spans="1:37" ht="15.75" customHeight="1">
+    <row r="94" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -5166,7 +5196,7 @@
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
     </row>
-    <row r="95" spans="1:37" ht="15.75" customHeight="1">
+    <row r="95" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -5205,7 +5235,7 @@
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
     </row>
-    <row r="96" spans="1:37" ht="15.75" customHeight="1">
+    <row r="96" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -5244,7 +5274,7 @@
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
     </row>
-    <row r="97" spans="1:37" ht="15.75" customHeight="1">
+    <row r="97" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -5283,7 +5313,7 @@
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
     </row>
-    <row r="98" spans="1:37" ht="15.75" customHeight="1">
+    <row r="98" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -5322,7 +5352,7 @@
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
     </row>
-    <row r="99" spans="1:37" ht="15.75" customHeight="1">
+    <row r="99" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5361,7 +5391,7 @@
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
     </row>
-    <row r="100" spans="1:37" ht="15.75" customHeight="1">
+    <row r="100" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -5400,7 +5430,7 @@
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
     </row>
-    <row r="101" spans="1:37" ht="15.75" customHeight="1">
+    <row r="101" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -5439,7 +5469,7 @@
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
     </row>
-    <row r="102" spans="1:37" ht="15.75" customHeight="1">
+    <row r="102" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -5478,7 +5508,7 @@
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
     </row>
-    <row r="103" spans="1:37" ht="15.75" customHeight="1">
+    <row r="103" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -5517,7 +5547,7 @@
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
     </row>
-    <row r="104" spans="1:37" ht="15.75" customHeight="1">
+    <row r="104" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -5556,7 +5586,7 @@
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
     </row>
-    <row r="105" spans="1:37" ht="15.75" customHeight="1">
+    <row r="105" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -5595,7 +5625,7 @@
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
     </row>
-    <row r="106" spans="1:37" ht="15.75" customHeight="1">
+    <row r="106" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -5634,7 +5664,7 @@
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
     </row>
-    <row r="107" spans="1:37" ht="15.75" customHeight="1">
+    <row r="107" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -5673,7 +5703,7 @@
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
     </row>
-    <row r="108" spans="1:37" ht="15.75" customHeight="1">
+    <row r="108" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -5712,7 +5742,7 @@
       <c r="AJ108" s="1"/>
       <c r="AK108" s="1"/>
     </row>
-    <row r="109" spans="1:37" ht="15.75" customHeight="1">
+    <row r="109" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -5751,7 +5781,7 @@
       <c r="AJ109" s="1"/>
       <c r="AK109" s="1"/>
     </row>
-    <row r="110" spans="1:37" ht="15.75" customHeight="1">
+    <row r="110" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -5790,7 +5820,7 @@
       <c r="AJ110" s="1"/>
       <c r="AK110" s="1"/>
     </row>
-    <row r="111" spans="1:37" ht="15.75" customHeight="1">
+    <row r="111" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -5829,7 +5859,7 @@
       <c r="AJ111" s="1"/>
       <c r="AK111" s="1"/>
     </row>
-    <row r="112" spans="1:37" ht="15.75" customHeight="1">
+    <row r="112" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -5868,7 +5898,7 @@
       <c r="AJ112" s="1"/>
       <c r="AK112" s="1"/>
     </row>
-    <row r="113" spans="1:37" ht="15.75" customHeight="1">
+    <row r="113" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -5907,7 +5937,7 @@
       <c r="AJ113" s="1"/>
       <c r="AK113" s="1"/>
     </row>
-    <row r="114" spans="1:37" ht="15.75" customHeight="1">
+    <row r="114" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -5946,7 +5976,7 @@
       <c r="AJ114" s="1"/>
       <c r="AK114" s="1"/>
     </row>
-    <row r="115" spans="1:37" ht="15.75" customHeight="1">
+    <row r="115" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -5985,7 +6015,7 @@
       <c r="AJ115" s="1"/>
       <c r="AK115" s="1"/>
     </row>
-    <row r="116" spans="1:37" ht="15.75" customHeight="1">
+    <row r="116" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -6024,7 +6054,7 @@
       <c r="AJ116" s="1"/>
       <c r="AK116" s="1"/>
     </row>
-    <row r="117" spans="1:37" ht="15.75" customHeight="1">
+    <row r="117" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -6063,7 +6093,7 @@
       <c r="AJ117" s="1"/>
       <c r="AK117" s="1"/>
     </row>
-    <row r="118" spans="1:37" ht="15.75" customHeight="1">
+    <row r="118" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -6102,7 +6132,7 @@
       <c r="AJ118" s="1"/>
       <c r="AK118" s="1"/>
     </row>
-    <row r="119" spans="1:37" ht="15.75" customHeight="1">
+    <row r="119" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -6141,7 +6171,7 @@
       <c r="AJ119" s="1"/>
       <c r="AK119" s="1"/>
     </row>
-    <row r="120" spans="1:37" ht="15.75" customHeight="1">
+    <row r="120" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -6180,7 +6210,7 @@
       <c r="AJ120" s="1"/>
       <c r="AK120" s="1"/>
     </row>
-    <row r="121" spans="1:37" ht="15.75" customHeight="1">
+    <row r="121" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -6219,7 +6249,7 @@
       <c r="AJ121" s="1"/>
       <c r="AK121" s="1"/>
     </row>
-    <row r="122" spans="1:37" ht="15.75" customHeight="1">
+    <row r="122" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -6258,7 +6288,7 @@
       <c r="AJ122" s="1"/>
       <c r="AK122" s="1"/>
     </row>
-    <row r="123" spans="1:37" ht="15.75" customHeight="1">
+    <row r="123" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -6297,7 +6327,7 @@
       <c r="AJ123" s="1"/>
       <c r="AK123" s="1"/>
     </row>
-    <row r="124" spans="1:37" ht="15.75" customHeight="1">
+    <row r="124" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -6336,7 +6366,7 @@
       <c r="AJ124" s="1"/>
       <c r="AK124" s="1"/>
     </row>
-    <row r="125" spans="1:37" ht="15.75" customHeight="1">
+    <row r="125" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -6375,7 +6405,7 @@
       <c r="AJ125" s="1"/>
       <c r="AK125" s="1"/>
     </row>
-    <row r="126" spans="1:37" ht="15.75" customHeight="1">
+    <row r="126" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -6414,7 +6444,7 @@
       <c r="AJ126" s="1"/>
       <c r="AK126" s="1"/>
     </row>
-    <row r="127" spans="1:37" ht="15.75" customHeight="1">
+    <row r="127" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -6453,7 +6483,7 @@
       <c r="AJ127" s="1"/>
       <c r="AK127" s="1"/>
     </row>
-    <row r="128" spans="1:37" ht="15.75" customHeight="1">
+    <row r="128" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -6492,7 +6522,7 @@
       <c r="AJ128" s="1"/>
       <c r="AK128" s="1"/>
     </row>
-    <row r="129" spans="1:37" ht="15.75" customHeight="1">
+    <row r="129" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -6531,7 +6561,7 @@
       <c r="AJ129" s="1"/>
       <c r="AK129" s="1"/>
     </row>
-    <row r="130" spans="1:37" ht="15.75" customHeight="1">
+    <row r="130" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -6570,7 +6600,7 @@
       <c r="AJ130" s="1"/>
       <c r="AK130" s="1"/>
     </row>
-    <row r="131" spans="1:37" ht="15.75" customHeight="1">
+    <row r="131" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -6609,7 +6639,7 @@
       <c r="AJ131" s="1"/>
       <c r="AK131" s="1"/>
     </row>
-    <row r="132" spans="1:37" ht="15.75" customHeight="1">
+    <row r="132" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -6648,7 +6678,7 @@
       <c r="AJ132" s="1"/>
       <c r="AK132" s="1"/>
     </row>
-    <row r="133" spans="1:37" ht="15.75" customHeight="1">
+    <row r="133" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -6687,7 +6717,7 @@
       <c r="AJ133" s="1"/>
       <c r="AK133" s="1"/>
     </row>
-    <row r="134" spans="1:37" ht="15.75" customHeight="1">
+    <row r="134" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -6726,7 +6756,7 @@
       <c r="AJ134" s="1"/>
       <c r="AK134" s="1"/>
     </row>
-    <row r="135" spans="1:37" ht="15.75" customHeight="1">
+    <row r="135" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -6765,7 +6795,7 @@
       <c r="AJ135" s="1"/>
       <c r="AK135" s="1"/>
     </row>
-    <row r="136" spans="1:37" ht="15.75" customHeight="1">
+    <row r="136" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -6804,7 +6834,7 @@
       <c r="AJ136" s="1"/>
       <c r="AK136" s="1"/>
     </row>
-    <row r="137" spans="1:37" ht="15.75" customHeight="1">
+    <row r="137" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -6843,7 +6873,7 @@
       <c r="AJ137" s="1"/>
       <c r="AK137" s="1"/>
     </row>
-    <row r="138" spans="1:37" ht="15.75" customHeight="1">
+    <row r="138" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -6882,7 +6912,7 @@
       <c r="AJ138" s="1"/>
       <c r="AK138" s="1"/>
     </row>
-    <row r="139" spans="1:37" ht="15.75" customHeight="1">
+    <row r="139" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -6921,7 +6951,7 @@
       <c r="AJ139" s="1"/>
       <c r="AK139" s="1"/>
     </row>
-    <row r="140" spans="1:37" ht="15.75" customHeight="1">
+    <row r="140" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -6960,7 +6990,7 @@
       <c r="AJ140" s="1"/>
       <c r="AK140" s="1"/>
     </row>
-    <row r="141" spans="1:37" ht="15.75" customHeight="1">
+    <row r="141" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -6999,7 +7029,7 @@
       <c r="AJ141" s="1"/>
       <c r="AK141" s="1"/>
     </row>
-    <row r="142" spans="1:37" ht="15.75" customHeight="1">
+    <row r="142" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -7038,7 +7068,7 @@
       <c r="AJ142" s="1"/>
       <c r="AK142" s="1"/>
     </row>
-    <row r="143" spans="1:37" ht="15.75" customHeight="1">
+    <row r="143" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -7077,7 +7107,7 @@
       <c r="AJ143" s="1"/>
       <c r="AK143" s="1"/>
     </row>
-    <row r="144" spans="1:37" ht="15.75" customHeight="1">
+    <row r="144" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -7116,7 +7146,7 @@
       <c r="AJ144" s="1"/>
       <c r="AK144" s="1"/>
     </row>
-    <row r="145" spans="1:37" ht="15.75" customHeight="1">
+    <row r="145" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -7155,7 +7185,7 @@
       <c r="AJ145" s="1"/>
       <c r="AK145" s="1"/>
     </row>
-    <row r="146" spans="1:37" ht="15.75" customHeight="1">
+    <row r="146" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -7194,7 +7224,7 @@
       <c r="AJ146" s="1"/>
       <c r="AK146" s="1"/>
     </row>
-    <row r="147" spans="1:37" ht="15.75" customHeight="1">
+    <row r="147" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -7233,7 +7263,7 @@
       <c r="AJ147" s="1"/>
       <c r="AK147" s="1"/>
     </row>
-    <row r="148" spans="1:37" ht="15.75" customHeight="1">
+    <row r="148" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -7272,7 +7302,7 @@
       <c r="AJ148" s="1"/>
       <c r="AK148" s="1"/>
     </row>
-    <row r="149" spans="1:37" ht="15.75" customHeight="1">
+    <row r="149" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -7311,7 +7341,7 @@
       <c r="AJ149" s="1"/>
       <c r="AK149" s="1"/>
     </row>
-    <row r="150" spans="1:37" ht="15.75" customHeight="1">
+    <row r="150" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -7350,7 +7380,7 @@
       <c r="AJ150" s="1"/>
       <c r="AK150" s="1"/>
     </row>
-    <row r="151" spans="1:37" ht="15.75" customHeight="1">
+    <row r="151" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -7389,7 +7419,7 @@
       <c r="AJ151" s="1"/>
       <c r="AK151" s="1"/>
     </row>
-    <row r="152" spans="1:37" ht="15.75" customHeight="1">
+    <row r="152" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -7428,7 +7458,7 @@
       <c r="AJ152" s="1"/>
       <c r="AK152" s="1"/>
     </row>
-    <row r="153" spans="1:37" ht="15.75" customHeight="1">
+    <row r="153" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -7467,7 +7497,7 @@
       <c r="AJ153" s="1"/>
       <c r="AK153" s="1"/>
     </row>
-    <row r="154" spans="1:37" ht="15.75" customHeight="1">
+    <row r="154" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -7506,7 +7536,7 @@
       <c r="AJ154" s="1"/>
       <c r="AK154" s="1"/>
     </row>
-    <row r="155" spans="1:37" ht="15.75" customHeight="1">
+    <row r="155" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -7545,7 +7575,7 @@
       <c r="AJ155" s="1"/>
       <c r="AK155" s="1"/>
     </row>
-    <row r="156" spans="1:37" ht="15.75" customHeight="1">
+    <row r="156" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -7584,7 +7614,7 @@
       <c r="AJ156" s="1"/>
       <c r="AK156" s="1"/>
     </row>
-    <row r="157" spans="1:37" ht="15.75" customHeight="1">
+    <row r="157" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -7623,7 +7653,7 @@
       <c r="AJ157" s="1"/>
       <c r="AK157" s="1"/>
     </row>
-    <row r="158" spans="1:37" ht="15.75" customHeight="1">
+    <row r="158" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -7662,7 +7692,7 @@
       <c r="AJ158" s="1"/>
       <c r="AK158" s="1"/>
     </row>
-    <row r="159" spans="1:37" ht="15.75" customHeight="1">
+    <row r="159" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -7701,7 +7731,7 @@
       <c r="AJ159" s="1"/>
       <c r="AK159" s="1"/>
     </row>
-    <row r="160" spans="1:37" ht="15.75" customHeight="1">
+    <row r="160" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -7740,7 +7770,7 @@
       <c r="AJ160" s="1"/>
       <c r="AK160" s="1"/>
     </row>
-    <row r="161" spans="1:37" ht="15.75" customHeight="1">
+    <row r="161" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -7779,7 +7809,7 @@
       <c r="AJ161" s="1"/>
       <c r="AK161" s="1"/>
     </row>
-    <row r="162" spans="1:37" ht="15.75" customHeight="1">
+    <row r="162" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -7818,7 +7848,7 @@
       <c r="AJ162" s="1"/>
       <c r="AK162" s="1"/>
     </row>
-    <row r="163" spans="1:37" ht="15.75" customHeight="1">
+    <row r="163" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -7857,7 +7887,7 @@
       <c r="AJ163" s="1"/>
       <c r="AK163" s="1"/>
     </row>
-    <row r="164" spans="1:37" ht="15.75" customHeight="1">
+    <row r="164" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -7896,7 +7926,7 @@
       <c r="AJ164" s="1"/>
       <c r="AK164" s="1"/>
     </row>
-    <row r="165" spans="1:37" ht="15.75" customHeight="1">
+    <row r="165" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -7935,7 +7965,7 @@
       <c r="AJ165" s="1"/>
       <c r="AK165" s="1"/>
     </row>
-    <row r="166" spans="1:37" ht="15.75" customHeight="1">
+    <row r="166" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -7974,7 +8004,7 @@
       <c r="AJ166" s="1"/>
       <c r="AK166" s="1"/>
     </row>
-    <row r="167" spans="1:37" ht="15.75" customHeight="1">
+    <row r="167" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -8013,7 +8043,7 @@
       <c r="AJ167" s="1"/>
       <c r="AK167" s="1"/>
     </row>
-    <row r="168" spans="1:37" ht="15.75" customHeight="1">
+    <row r="168" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -8052,7 +8082,7 @@
       <c r="AJ168" s="1"/>
       <c r="AK168" s="1"/>
     </row>
-    <row r="169" spans="1:37" ht="15.75" customHeight="1">
+    <row r="169" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -8091,7 +8121,7 @@
       <c r="AJ169" s="1"/>
       <c r="AK169" s="1"/>
     </row>
-    <row r="170" spans="1:37" ht="15.75" customHeight="1">
+    <row r="170" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -8130,7 +8160,7 @@
       <c r="AJ170" s="1"/>
       <c r="AK170" s="1"/>
     </row>
-    <row r="171" spans="1:37" ht="15.75" customHeight="1">
+    <row r="171" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -8169,7 +8199,7 @@
       <c r="AJ171" s="1"/>
       <c r="AK171" s="1"/>
     </row>
-    <row r="172" spans="1:37" ht="15.75" customHeight="1">
+    <row r="172" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -8208,7 +8238,7 @@
       <c r="AJ172" s="1"/>
       <c r="AK172" s="1"/>
     </row>
-    <row r="173" spans="1:37" ht="15.75" customHeight="1">
+    <row r="173" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -8247,7 +8277,7 @@
       <c r="AJ173" s="1"/>
       <c r="AK173" s="1"/>
     </row>
-    <row r="174" spans="1:37" ht="15.75" customHeight="1">
+    <row r="174" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -8286,7 +8316,7 @@
       <c r="AJ174" s="1"/>
       <c r="AK174" s="1"/>
     </row>
-    <row r="175" spans="1:37" ht="15.75" customHeight="1">
+    <row r="175" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -8325,7 +8355,7 @@
       <c r="AJ175" s="1"/>
       <c r="AK175" s="1"/>
     </row>
-    <row r="176" spans="1:37" ht="15.75" customHeight="1">
+    <row r="176" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -8364,7 +8394,7 @@
       <c r="AJ176" s="1"/>
       <c r="AK176" s="1"/>
     </row>
-    <row r="177" spans="1:37" ht="15.75" customHeight="1">
+    <row r="177" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -8403,7 +8433,7 @@
       <c r="AJ177" s="1"/>
       <c r="AK177" s="1"/>
     </row>
-    <row r="178" spans="1:37" ht="15.75" customHeight="1">
+    <row r="178" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -8442,7 +8472,7 @@
       <c r="AJ178" s="1"/>
       <c r="AK178" s="1"/>
     </row>
-    <row r="179" spans="1:37" ht="15.75" customHeight="1">
+    <row r="179" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -8481,7 +8511,7 @@
       <c r="AJ179" s="1"/>
       <c r="AK179" s="1"/>
     </row>
-    <row r="180" spans="1:37" ht="15.75" customHeight="1">
+    <row r="180" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -8520,7 +8550,7 @@
       <c r="AJ180" s="1"/>
       <c r="AK180" s="1"/>
     </row>
-    <row r="181" spans="1:37" ht="15.75" customHeight="1">
+    <row r="181" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -8559,7 +8589,7 @@
       <c r="AJ181" s="1"/>
       <c r="AK181" s="1"/>
     </row>
-    <row r="182" spans="1:37" ht="15.75" customHeight="1">
+    <row r="182" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -8598,7 +8628,7 @@
       <c r="AJ182" s="1"/>
       <c r="AK182" s="1"/>
     </row>
-    <row r="183" spans="1:37" ht="15.75" customHeight="1">
+    <row r="183" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -8637,7 +8667,7 @@
       <c r="AJ183" s="1"/>
       <c r="AK183" s="1"/>
     </row>
-    <row r="184" spans="1:37" ht="15.75" customHeight="1">
+    <row r="184" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -8676,7 +8706,7 @@
       <c r="AJ184" s="1"/>
       <c r="AK184" s="1"/>
     </row>
-    <row r="185" spans="1:37" ht="15.75" customHeight="1">
+    <row r="185" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -8715,7 +8745,7 @@
       <c r="AJ185" s="1"/>
       <c r="AK185" s="1"/>
     </row>
-    <row r="186" spans="1:37" ht="15.75" customHeight="1">
+    <row r="186" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -8754,7 +8784,7 @@
       <c r="AJ186" s="1"/>
       <c r="AK186" s="1"/>
     </row>
-    <row r="187" spans="1:37" ht="15.75" customHeight="1">
+    <row r="187" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -8793,7 +8823,7 @@
       <c r="AJ187" s="1"/>
       <c r="AK187" s="1"/>
     </row>
-    <row r="188" spans="1:37" ht="15.75" customHeight="1">
+    <row r="188" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -8832,7 +8862,7 @@
       <c r="AJ188" s="1"/>
       <c r="AK188" s="1"/>
     </row>
-    <row r="189" spans="1:37" ht="15.75" customHeight="1">
+    <row r="189" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -8871,7 +8901,7 @@
       <c r="AJ189" s="1"/>
       <c r="AK189" s="1"/>
     </row>
-    <row r="190" spans="1:37" ht="15.75" customHeight="1">
+    <row r="190" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -8910,7 +8940,7 @@
       <c r="AJ190" s="1"/>
       <c r="AK190" s="1"/>
     </row>
-    <row r="191" spans="1:37" ht="15.75" customHeight="1">
+    <row r="191" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -8949,7 +8979,7 @@
       <c r="AJ191" s="1"/>
       <c r="AK191" s="1"/>
     </row>
-    <row r="192" spans="1:37" ht="15.75" customHeight="1">
+    <row r="192" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -8988,7 +9018,7 @@
       <c r="AJ192" s="1"/>
       <c r="AK192" s="1"/>
     </row>
-    <row r="193" spans="1:37" ht="15.75" customHeight="1">
+    <row r="193" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -9027,7 +9057,7 @@
       <c r="AJ193" s="1"/>
       <c r="AK193" s="1"/>
     </row>
-    <row r="194" spans="1:37" ht="15.75" customHeight="1">
+    <row r="194" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -9066,7 +9096,7 @@
       <c r="AJ194" s="1"/>
       <c r="AK194" s="1"/>
     </row>
-    <row r="195" spans="1:37" ht="15.75" customHeight="1">
+    <row r="195" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -9105,7 +9135,7 @@
       <c r="AJ195" s="1"/>
       <c r="AK195" s="1"/>
     </row>
-    <row r="196" spans="1:37" ht="15.75" customHeight="1">
+    <row r="196" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -9144,7 +9174,7 @@
       <c r="AJ196" s="1"/>
       <c r="AK196" s="1"/>
     </row>
-    <row r="197" spans="1:37" ht="15.75" customHeight="1">
+    <row r="197" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -9183,7 +9213,7 @@
       <c r="AJ197" s="1"/>
       <c r="AK197" s="1"/>
     </row>
-    <row r="198" spans="1:37" ht="15.75" customHeight="1">
+    <row r="198" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -9222,7 +9252,7 @@
       <c r="AJ198" s="1"/>
       <c r="AK198" s="1"/>
     </row>
-    <row r="199" spans="1:37" ht="15.75" customHeight="1">
+    <row r="199" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -9261,7 +9291,7 @@
       <c r="AJ199" s="1"/>
       <c r="AK199" s="1"/>
     </row>
-    <row r="200" spans="1:37" ht="15.75" customHeight="1">
+    <row r="200" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -9300,7 +9330,7 @@
       <c r="AJ200" s="1"/>
       <c r="AK200" s="1"/>
     </row>
-    <row r="201" spans="1:37" ht="15.75" customHeight="1">
+    <row r="201" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -9339,7 +9369,7 @@
       <c r="AJ201" s="1"/>
       <c r="AK201" s="1"/>
     </row>
-    <row r="202" spans="1:37" ht="15.75" customHeight="1">
+    <row r="202" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -9378,7 +9408,7 @@
       <c r="AJ202" s="1"/>
       <c r="AK202" s="1"/>
     </row>
-    <row r="203" spans="1:37" ht="15.75" customHeight="1">
+    <row r="203" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -9417,7 +9447,7 @@
       <c r="AJ203" s="1"/>
       <c r="AK203" s="1"/>
     </row>
-    <row r="204" spans="1:37" ht="15.75" customHeight="1">
+    <row r="204" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -9456,7 +9486,7 @@
       <c r="AJ204" s="1"/>
       <c r="AK204" s="1"/>
     </row>
-    <row r="205" spans="1:37" ht="15.75" customHeight="1">
+    <row r="205" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -9495,7 +9525,7 @@
       <c r="AJ205" s="1"/>
       <c r="AK205" s="1"/>
     </row>
-    <row r="206" spans="1:37" ht="15.75" customHeight="1">
+    <row r="206" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -9534,7 +9564,7 @@
       <c r="AJ206" s="1"/>
       <c r="AK206" s="1"/>
     </row>
-    <row r="207" spans="1:37" ht="15.75" customHeight="1">
+    <row r="207" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -9573,7 +9603,7 @@
       <c r="AJ207" s="1"/>
       <c r="AK207" s="1"/>
     </row>
-    <row r="208" spans="1:37" ht="15.75" customHeight="1">
+    <row r="208" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -9612,7 +9642,7 @@
       <c r="AJ208" s="1"/>
       <c r="AK208" s="1"/>
     </row>
-    <row r="209" spans="1:37" ht="15.75" customHeight="1">
+    <row r="209" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -9651,7 +9681,7 @@
       <c r="AJ209" s="1"/>
       <c r="AK209" s="1"/>
     </row>
-    <row r="210" spans="1:37" ht="15.75" customHeight="1">
+    <row r="210" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -9690,7 +9720,7 @@
       <c r="AJ210" s="1"/>
       <c r="AK210" s="1"/>
     </row>
-    <row r="211" spans="1:37" ht="15.75" customHeight="1">
+    <row r="211" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -9729,7 +9759,7 @@
       <c r="AJ211" s="1"/>
       <c r="AK211" s="1"/>
     </row>
-    <row r="212" spans="1:37" ht="15.75" customHeight="1">
+    <row r="212" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -9768,7 +9798,7 @@
       <c r="AJ212" s="1"/>
       <c r="AK212" s="1"/>
     </row>
-    <row r="213" spans="1:37" ht="15.75" customHeight="1">
+    <row r="213" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -9807,7 +9837,7 @@
       <c r="AJ213" s="1"/>
       <c r="AK213" s="1"/>
     </row>
-    <row r="214" spans="1:37" ht="15.75" customHeight="1">
+    <row r="214" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -9846,7 +9876,7 @@
       <c r="AJ214" s="1"/>
       <c r="AK214" s="1"/>
     </row>
-    <row r="215" spans="1:37" ht="15.75" customHeight="1">
+    <row r="215" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -9885,7 +9915,7 @@
       <c r="AJ215" s="1"/>
       <c r="AK215" s="1"/>
     </row>
-    <row r="216" spans="1:37" ht="15.75" customHeight="1">
+    <row r="216" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -9924,7 +9954,7 @@
       <c r="AJ216" s="1"/>
       <c r="AK216" s="1"/>
     </row>
-    <row r="217" spans="1:37" ht="15.75" customHeight="1">
+    <row r="217" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -9963,7 +9993,7 @@
       <c r="AJ217" s="1"/>
       <c r="AK217" s="1"/>
     </row>
-    <row r="218" spans="1:37" ht="15.75" customHeight="1">
+    <row r="218" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -10002,7 +10032,7 @@
       <c r="AJ218" s="1"/>
       <c r="AK218" s="1"/>
     </row>
-    <row r="219" spans="1:37" ht="15.75" customHeight="1">
+    <row r="219" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -10041,7 +10071,7 @@
       <c r="AJ219" s="1"/>
       <c r="AK219" s="1"/>
     </row>
-    <row r="220" spans="1:37" ht="15.75" customHeight="1">
+    <row r="220" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -10080,7 +10110,7 @@
       <c r="AJ220" s="1"/>
       <c r="AK220" s="1"/>
     </row>
-    <row r="221" spans="1:37" ht="15.75" customHeight="1">
+    <row r="221" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -10119,7 +10149,7 @@
       <c r="AJ221" s="1"/>
       <c r="AK221" s="1"/>
     </row>
-    <row r="222" spans="1:37" ht="15.75" customHeight="1">
+    <row r="222" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -10158,7 +10188,7 @@
       <c r="AJ222" s="1"/>
       <c r="AK222" s="1"/>
     </row>
-    <row r="223" spans="1:37" ht="15.75" customHeight="1">
+    <row r="223" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -10197,7 +10227,7 @@
       <c r="AJ223" s="1"/>
       <c r="AK223" s="1"/>
     </row>
-    <row r="224" spans="1:37" ht="15.75" customHeight="1">
+    <row r="224" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -10236,7 +10266,7 @@
       <c r="AJ224" s="1"/>
       <c r="AK224" s="1"/>
     </row>
-    <row r="225" spans="1:37" ht="15.75" customHeight="1">
+    <row r="225" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -10275,7 +10305,7 @@
       <c r="AJ225" s="1"/>
       <c r="AK225" s="1"/>
     </row>
-    <row r="226" spans="1:37" ht="15.75" customHeight="1">
+    <row r="226" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -10314,7 +10344,7 @@
       <c r="AJ226" s="1"/>
       <c r="AK226" s="1"/>
     </row>
-    <row r="227" spans="1:37" ht="15.75" customHeight="1">
+    <row r="227" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -10353,7 +10383,7 @@
       <c r="AJ227" s="1"/>
       <c r="AK227" s="1"/>
     </row>
-    <row r="228" spans="1:37" ht="15.75" customHeight="1">
+    <row r="228" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -10392,7 +10422,7 @@
       <c r="AJ228" s="1"/>
       <c r="AK228" s="1"/>
     </row>
-    <row r="229" spans="1:37" ht="15.75" customHeight="1">
+    <row r="229" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -10431,7 +10461,7 @@
       <c r="AJ229" s="1"/>
       <c r="AK229" s="1"/>
     </row>
-    <row r="230" spans="1:37" ht="15.75" customHeight="1">
+    <row r="230" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -10470,7 +10500,7 @@
       <c r="AJ230" s="1"/>
       <c r="AK230" s="1"/>
     </row>
-    <row r="231" spans="1:37" ht="15.75" customHeight="1">
+    <row r="231" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -10509,7 +10539,7 @@
       <c r="AJ231" s="1"/>
       <c r="AK231" s="1"/>
     </row>
-    <row r="232" spans="1:37" ht="15.75" customHeight="1">
+    <row r="232" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -10548,7 +10578,7 @@
       <c r="AJ232" s="1"/>
       <c r="AK232" s="1"/>
     </row>
-    <row r="233" spans="1:37" ht="15.75" customHeight="1">
+    <row r="233" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -10587,7 +10617,7 @@
       <c r="AJ233" s="1"/>
       <c r="AK233" s="1"/>
     </row>
-    <row r="234" spans="1:37" ht="15.75" customHeight="1">
+    <row r="234" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -10626,7 +10656,7 @@
       <c r="AJ234" s="1"/>
       <c r="AK234" s="1"/>
     </row>
-    <row r="235" spans="1:37" ht="15.75" customHeight="1">
+    <row r="235" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -10665,7 +10695,7 @@
       <c r="AJ235" s="1"/>
       <c r="AK235" s="1"/>
     </row>
-    <row r="236" spans="1:37" ht="15.75" customHeight="1">
+    <row r="236" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -10704,770 +10734,770 @@
       <c r="AJ236" s="1"/>
       <c r="AK236" s="1"/>
     </row>
-    <row r="237" spans="1:37" ht="15.75" customHeight="1"/>
-    <row r="238" spans="1:37" ht="15.75" customHeight="1"/>
-    <row r="239" spans="1:37" ht="15.75" customHeight="1"/>
-    <row r="240" spans="1:37" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="237" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -11480,14 +11510,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="D7:R35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="17.19921875" customWidth="1"/>
-    <col min="6" max="6" width="15.796875" customWidth="1"/>
-    <col min="7" max="18" width="3.796875" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="18" width="3.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="4:18">
+    <row r="7" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -11528,7 +11558,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="4:18">
+    <row r="8" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D8" s="2"/>
       <c r="E8" s="19" t="s">
         <v>81</v>
@@ -11551,7 +11581,7 @@
       <c r="Q8" s="40"/>
       <c r="R8" s="41"/>
     </row>
-    <row r="9" spans="4:18">
+    <row r="9" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D9" s="2"/>
       <c r="E9" s="19" t="s">
         <v>81</v>
@@ -11578,7 +11608,7 @@
       <c r="Q9" s="45"/>
       <c r="R9" s="46"/>
     </row>
-    <row r="10" spans="4:18">
+    <row r="10" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D10" s="2"/>
       <c r="E10" s="19" t="s">
         <v>81</v>
@@ -11607,7 +11637,7 @@
       <c r="Q10" s="45"/>
       <c r="R10" s="46"/>
     </row>
-    <row r="11" spans="4:18">
+    <row r="11" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D11" s="2"/>
       <c r="E11" s="19" t="s">
         <v>81</v>
@@ -11640,7 +11670,7 @@
       <c r="Q11" s="45"/>
       <c r="R11" s="46"/>
     </row>
-    <row r="12" spans="4:18">
+    <row r="12" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D12" s="2"/>
       <c r="E12" s="47" t="s">
         <v>83</v>
@@ -11663,7 +11693,7 @@
       <c r="Q12" s="45"/>
       <c r="R12" s="46"/>
     </row>
-    <row r="13" spans="4:18">
+    <row r="13" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D13" s="2"/>
       <c r="E13" s="19" t="s">
         <v>81</v>
@@ -11700,7 +11730,7 @@
       <c r="Q13" s="45"/>
       <c r="R13" s="46"/>
     </row>
-    <row r="14" spans="4:18">
+    <row r="14" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D14" s="2"/>
       <c r="E14" s="19" t="s">
         <v>81</v>
@@ -11729,7 +11759,7 @@
       <c r="Q14" s="45"/>
       <c r="R14" s="46"/>
     </row>
-    <row r="15" spans="4:18">
+    <row r="15" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D15" s="2"/>
       <c r="E15" s="19" t="s">
         <v>81</v>
@@ -11766,7 +11796,7 @@
       <c r="Q15" s="45"/>
       <c r="R15" s="46"/>
     </row>
-    <row r="16" spans="4:18">
+    <row r="16" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D16" s="2"/>
       <c r="E16" s="19" t="s">
         <v>81</v>
@@ -11805,7 +11835,7 @@
       <c r="Q16" s="45"/>
       <c r="R16" s="46"/>
     </row>
-    <row r="17" spans="4:18">
+    <row r="17" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D17" s="1"/>
       <c r="E17" s="19" t="s">
         <v>81</v>
@@ -11838,7 +11868,7 @@
       <c r="Q17" s="45"/>
       <c r="R17" s="46"/>
     </row>
-    <row r="18" spans="4:18">
+    <row r="18" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D18" s="1"/>
       <c r="E18" s="47" t="s">
         <v>83</v>
@@ -11877,7 +11907,7 @@
       </c>
       <c r="R18" s="46"/>
     </row>
-    <row r="19" spans="4:18">
+    <row r="19" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D19" s="1"/>
       <c r="E19" s="47" t="s">
         <v>83</v>
@@ -11918,7 +11948,7 @@
       <c r="Q19" s="45"/>
       <c r="R19" s="46"/>
     </row>
-    <row r="20" spans="4:18">
+    <row r="20" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D20" s="1"/>
       <c r="E20" s="47" t="s">
         <v>83</v>
@@ -11959,7 +11989,7 @@
       <c r="Q20" s="45"/>
       <c r="R20" s="46"/>
     </row>
-    <row r="21" spans="4:18">
+    <row r="21" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D21" s="1"/>
       <c r="E21" s="47" t="s">
         <v>83</v>
@@ -11982,7 +12012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="4:18">
+    <row r="22" spans="4:18" x14ac:dyDescent="0.2">
       <c r="D22" s="1"/>
       <c r="E22" s="47" t="s">
         <v>83</v>
@@ -12007,7 +12037,7 @@
       <c r="Q22" s="45"/>
       <c r="R22" s="54"/>
     </row>
-    <row r="25" spans="4:18">
+    <row r="25" spans="4:18" x14ac:dyDescent="0.2">
       <c r="E25" s="55" t="s">
         <v>87</v>
       </c>
@@ -12015,7 +12045,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="4:18">
+    <row r="26" spans="4:18" x14ac:dyDescent="0.2">
       <c r="E26" s="14" t="s">
         <v>22</v>
       </c>
@@ -12023,7 +12053,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="4:18">
+    <row r="27" spans="4:18" x14ac:dyDescent="0.2">
       <c r="I27" s="55">
         <v>1</v>
       </c>
@@ -12031,7 +12061,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="5:18">
+    <row r="35" spans="5:18" x14ac:dyDescent="0.2">
       <c r="E35" s="19" t="s">
         <v>81</v>
       </c>
@@ -12066,13 +12096,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Q26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="31.8984375" customWidth="1"/>
-    <col min="4" max="5" width="24.09765625" customWidth="1"/>
+    <col min="1" max="3" width="31.83203125" customWidth="1"/>
+    <col min="4" max="10" width="29.5" customWidth="1"/>
+    <col min="11" max="11" width="43.83203125" customWidth="1"/>
+    <col min="12" max="16" width="29.5" customWidth="1"/>
+    <col min="17" max="17" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="1" spans="1:17" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="57"/>
       <c r="B1" s="63" t="s">
         <v>92</v>
@@ -12081,10 +12114,10 @@
         <v>95</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="F1" s="58" t="s">
         <v>6</v>
@@ -12093,39 +12126,39 @@
         <v>96</v>
       </c>
       <c r="H1" s="58" t="s">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="I1" s="58" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J1" s="58" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="K1" s="58" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="L1" s="58" t="s">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="M1" s="58" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="N1" s="58" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="58" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P1" s="58" t="s">
         <v>14</v>
       </c>
       <c r="Q1" s="58" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" thickBot="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B2" s="65" t="s">
         <v>93</v>
@@ -12133,38 +12166,26 @@
       <c r="C2" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="66">
-        <v>7</v>
-      </c>
-      <c r="E2" s="67">
-        <v>6</v>
-      </c>
-      <c r="F2" s="67">
-        <v>5</v>
-      </c>
-      <c r="G2" s="67">
-        <v>4</v>
-      </c>
-      <c r="H2" s="67">
-        <v>3</v>
-      </c>
-      <c r="I2" s="68"/>
-      <c r="J2" s="67">
-        <v>2</v>
-      </c>
-      <c r="K2" s="69">
+      <c r="D2" s="69">
         <v>1</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68"/>
-    </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" thickBot="1">
+      <c r="E2" s="72"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+    </row>
+    <row r="3" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B3" s="65" t="s">
         <v>93</v>
@@ -12172,10 +12193,10 @@
       <c r="C3" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="70">
+      <c r="D3" s="69">
         <v>1</v>
       </c>
-      <c r="E3" s="61"/>
+      <c r="E3" s="72"/>
       <c r="F3" s="61"/>
       <c r="G3" s="61"/>
       <c r="H3" s="61"/>
@@ -12189,9 +12210,9 @@
       <c r="P3" s="61"/>
       <c r="Q3" s="61"/>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="4" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="59" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="65" t="s">
         <v>93</v>
@@ -12199,15 +12220,11 @@
       <c r="C4" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="71">
-        <v>3</v>
-      </c>
-      <c r="E4" s="60">
-        <v>2</v>
-      </c>
-      <c r="F4" s="62">
+      <c r="D4" s="69">
         <v>1</v>
       </c>
+      <c r="E4" s="72"/>
+      <c r="F4" s="61"/>
       <c r="G4" s="61"/>
       <c r="H4" s="61"/>
       <c r="I4" s="61"/>
@@ -12220,9 +12237,9 @@
       <c r="P4" s="61"/>
       <c r="Q4" s="61"/>
     </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="5" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="65" t="s">
         <v>93</v>
@@ -12231,10 +12248,14 @@
         <v>16</v>
       </c>
       <c r="D5" s="70">
+        <v>3</v>
+      </c>
+      <c r="E5" s="60">
+        <v>2</v>
+      </c>
+      <c r="F5" s="62">
         <v>1</v>
       </c>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
       <c r="G5" s="61"/>
       <c r="H5" s="61"/>
       <c r="I5" s="61"/>
@@ -12247,9 +12268,9 @@
       <c r="P5" s="61"/>
       <c r="Q5" s="61"/>
     </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="6" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="59" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B6" s="65" t="s">
         <v>93</v>
@@ -12257,11 +12278,11 @@
       <c r="C6" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="71">
-        <v>4</v>
+      <c r="D6" s="70">
+        <v>3</v>
       </c>
       <c r="E6" s="60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="61"/>
       <c r="G6" s="61"/>
@@ -12269,20 +12290,18 @@
       <c r="I6" s="61"/>
       <c r="J6" s="61"/>
       <c r="K6" s="61"/>
-      <c r="L6" s="60">
-        <v>2</v>
-      </c>
-      <c r="M6" s="62">
+      <c r="L6" s="62">
         <v>1</v>
       </c>
+      <c r="M6" s="61"/>
       <c r="N6" s="61"/>
       <c r="O6" s="61"/>
       <c r="P6" s="61"/>
       <c r="Q6" s="61"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="7" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="59" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B7" s="65" t="s">
         <v>93</v>
@@ -12290,26 +12309,36 @@
       <c r="C7" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="66">
+        <v>6</v>
+      </c>
+      <c r="E7" s="67">
+        <v>5</v>
+      </c>
+      <c r="F7" s="67">
+        <v>4</v>
+      </c>
+      <c r="G7" s="67">
+        <v>3</v>
+      </c>
+      <c r="H7" s="68"/>
+      <c r="I7" s="67">
+        <v>2</v>
+      </c>
+      <c r="J7" s="62">
         <v>1</v>
       </c>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="61"/>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" thickBot="1">
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="68"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="68"/>
+      <c r="Q7" s="68"/>
+    </row>
+    <row r="8" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="B8" s="56" t="s">
         <v>94</v>
@@ -12317,8 +12346,8 @@
       <c r="C8" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="72"/>
-      <c r="E8" s="61"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="72"/>
       <c r="F8" s="61"/>
       <c r="G8" s="61"/>
       <c r="H8" s="61"/>
@@ -12334,7 +12363,7 @@
       <c r="P8" s="61"/>
       <c r="Q8" s="61"/>
     </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="9" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
         <v>31</v>
       </c>
@@ -12344,40 +12373,24 @@
       <c r="C9" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="71">
-        <v>9</v>
-      </c>
-      <c r="E9" s="60">
-        <v>8</v>
-      </c>
-      <c r="F9" s="60">
-        <v>7</v>
-      </c>
-      <c r="G9" s="60">
-        <v>6</v>
-      </c>
-      <c r="H9" s="60">
-        <v>5</v>
-      </c>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
       <c r="I9" s="61"/>
-      <c r="J9" s="60">
-        <v>4</v>
-      </c>
-      <c r="K9" s="60">
-        <v>3</v>
-      </c>
-      <c r="L9" s="60">
-        <v>2</v>
-      </c>
-      <c r="M9" s="62">
+      <c r="J9" s="61"/>
+      <c r="K9" s="62">
         <v>1</v>
       </c>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
       <c r="N9" s="61"/>
       <c r="O9" s="61"/>
       <c r="P9" s="61"/>
       <c r="Q9" s="61"/>
     </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="10" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
         <v>34</v>
       </c>
@@ -12387,24 +12400,16 @@
       <c r="C10" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="71">
-        <v>6</v>
-      </c>
-      <c r="E10" s="60">
-        <v>5</v>
-      </c>
-      <c r="F10" s="60">
-        <v>4</v>
-      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
       <c r="G10" s="60">
-        <v>3</v>
-      </c>
-      <c r="H10" s="60">
         <v>2</v>
       </c>
-      <c r="I10" s="62">
+      <c r="H10" s="62">
         <v>1</v>
       </c>
+      <c r="I10" s="61"/>
       <c r="J10" s="61"/>
       <c r="K10" s="61"/>
       <c r="L10" s="61"/>
@@ -12414,9 +12419,9 @@
       <c r="P10" s="61"/>
       <c r="Q10" s="61"/>
     </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="11" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B11" s="65" t="s">
         <v>93</v>
@@ -12424,42 +12429,46 @@
       <c r="C11" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="71">
+      <c r="D11" s="70">
+        <v>12</v>
+      </c>
+      <c r="E11" s="70">
+        <v>11</v>
+      </c>
+      <c r="F11" s="60">
+        <v>10</v>
+      </c>
+      <c r="G11" s="60">
         <v>9</v>
       </c>
-      <c r="E11" s="60">
-        <v>8</v>
-      </c>
-      <c r="F11" s="60">
+      <c r="H11" s="60">
         <v>7</v>
       </c>
-      <c r="G11" s="60">
+      <c r="I11" s="60">
         <v>6</v>
       </c>
-      <c r="H11" s="60">
+      <c r="J11" s="60">
         <v>5</v>
       </c>
-      <c r="I11" s="61"/>
-      <c r="J11" s="60">
+      <c r="K11" s="60">
         <v>4</v>
       </c>
-      <c r="K11" s="60">
+      <c r="L11" s="60">
         <v>3</v>
       </c>
-      <c r="L11" s="60">
+      <c r="M11" s="60">
         <v>2</v>
       </c>
-      <c r="M11" s="62">
+      <c r="N11" s="61"/>
+      <c r="O11" s="62">
         <v>1</v>
       </c>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61"/>
       <c r="P11" s="61"/>
       <c r="Q11" s="61"/>
     </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="12" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" s="65" t="s">
         <v>93</v>
@@ -12467,17 +12476,17 @@
       <c r="C12" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="71">
+      <c r="D12" s="70">
+        <v>12</v>
+      </c>
+      <c r="E12" s="70">
         <v>11</v>
       </c>
-      <c r="E12" s="60">
+      <c r="F12" s="60">
         <v>10</v>
       </c>
-      <c r="F12" s="60">
+      <c r="G12" s="60">
         <v>9</v>
-      </c>
-      <c r="G12" s="60">
-        <v>8</v>
       </c>
       <c r="H12" s="60">
         <v>7</v>
@@ -12504,9 +12513,9 @@
       <c r="P12" s="61"/>
       <c r="Q12" s="61"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="13" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="59" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B13" s="65" t="s">
         <v>93</v>
@@ -12514,17 +12523,17 @@
       <c r="C13" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="71">
+      <c r="D13" s="70">
+        <v>12</v>
+      </c>
+      <c r="E13" s="70">
         <v>11</v>
       </c>
-      <c r="E13" s="60">
+      <c r="F13" s="60">
         <v>10</v>
       </c>
-      <c r="F13" s="60">
+      <c r="G13" s="60">
         <v>9</v>
-      </c>
-      <c r="G13" s="60">
-        <v>8</v>
       </c>
       <c r="H13" s="60">
         <v>7</v>
@@ -12551,9 +12560,9 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="14" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="59" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B14" s="65" t="s">
         <v>93</v>
@@ -12561,42 +12570,46 @@
       <c r="C14" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="71">
+      <c r="D14" s="70">
+        <v>12</v>
+      </c>
+      <c r="E14" s="70">
         <v>11</v>
       </c>
-      <c r="E14" s="60">
+      <c r="F14" s="60">
         <v>10</v>
       </c>
-      <c r="F14" s="60">
+      <c r="G14" s="60">
         <v>9</v>
       </c>
-      <c r="G14" s="60">
-        <v>8</v>
-      </c>
       <c r="H14" s="60">
+        <v>7</v>
+      </c>
+      <c r="I14" s="60">
+        <v>6</v>
+      </c>
+      <c r="J14" s="60">
         <v>5</v>
       </c>
-      <c r="I14" s="61"/>
-      <c r="J14" s="60">
+      <c r="K14" s="60">
         <v>4</v>
       </c>
-      <c r="K14" s="60">
+      <c r="L14" s="60">
         <v>3</v>
       </c>
-      <c r="L14" s="60">
+      <c r="M14" s="60">
         <v>2</v>
       </c>
-      <c r="M14" s="62">
+      <c r="N14" s="61"/>
+      <c r="O14" s="62">
         <v>1</v>
       </c>
-      <c r="N14" s="61"/>
-      <c r="O14" s="61"/>
       <c r="P14" s="61"/>
       <c r="Q14" s="61"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="15" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="59" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B15" s="65" t="s">
         <v>93</v>
@@ -12604,17 +12617,17 @@
       <c r="C15" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="71">
+      <c r="D15" s="70">
+        <v>12</v>
+      </c>
+      <c r="E15" s="70">
         <v>11</v>
       </c>
-      <c r="E15" s="60">
+      <c r="F15" s="60">
         <v>10</v>
       </c>
-      <c r="F15" s="60">
+      <c r="G15" s="60">
         <v>9</v>
-      </c>
-      <c r="G15" s="60">
-        <v>8</v>
       </c>
       <c r="H15" s="60">
         <v>7</v>
@@ -12641,9 +12654,9 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="16" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="59" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B16" s="65" t="s">
         <v>93</v>
@@ -12651,46 +12664,38 @@
       <c r="C16" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="71">
-        <v>11</v>
+      <c r="D16" s="70">
+        <v>7</v>
       </c>
       <c r="E16" s="60">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" s="60">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G16" s="60">
-        <v>8</v>
-      </c>
-      <c r="H16" s="60">
-        <v>7</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H16" s="61"/>
       <c r="I16" s="60">
-        <v>6</v>
-      </c>
-      <c r="J16" s="60">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J16" s="61"/>
       <c r="K16" s="60">
-        <v>4</v>
-      </c>
-      <c r="L16" s="60">
-        <v>3</v>
-      </c>
-      <c r="M16" s="60">
         <v>2</v>
       </c>
+      <c r="L16" s="62">
+        <v>1</v>
+      </c>
+      <c r="M16" s="61"/>
       <c r="N16" s="61"/>
-      <c r="O16" s="62">
-        <v>1</v>
-      </c>
+      <c r="O16" s="61"/>
       <c r="P16" s="61"/>
       <c r="Q16" s="61"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="17" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="59" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B17" s="65" t="s">
         <v>93</v>
@@ -12698,44 +12703,36 @@
       <c r="C17" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="71">
-        <v>11</v>
+      <c r="D17" s="70">
+        <v>7</v>
       </c>
       <c r="E17" s="60">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" s="60">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G17" s="60">
-        <v>8</v>
-      </c>
-      <c r="H17" s="60">
-        <v>7</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H17" s="61"/>
       <c r="I17" s="60">
-        <v>6</v>
-      </c>
-      <c r="J17" s="60">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J17" s="61"/>
       <c r="K17" s="60">
-        <v>4</v>
-      </c>
-      <c r="L17" s="60">
-        <v>3</v>
-      </c>
-      <c r="M17" s="60">
         <v>2</v>
       </c>
+      <c r="L17" s="62">
+        <v>1</v>
+      </c>
+      <c r="M17" s="61"/>
       <c r="N17" s="61"/>
-      <c r="O17" s="62">
-        <v>1</v>
-      </c>
+      <c r="O17" s="61"/>
       <c r="P17" s="61"/>
       <c r="Q17" s="61"/>
     </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="18" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="59" t="s">
         <v>53</v>
       </c>
@@ -12745,34 +12742,42 @@
       <c r="C18" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="71">
+      <c r="D18" s="70">
+        <v>11</v>
+      </c>
+      <c r="E18" s="60">
+        <v>10</v>
+      </c>
+      <c r="F18" s="60">
+        <v>9</v>
+      </c>
+      <c r="G18" s="60">
+        <v>7</v>
+      </c>
+      <c r="H18" s="60">
         <v>6</v>
       </c>
-      <c r="E18" s="60">
+      <c r="I18" s="60">
         <v>5</v>
       </c>
-      <c r="F18" s="60">
+      <c r="J18" s="60">
         <v>4</v>
       </c>
-      <c r="G18" s="60">
+      <c r="K18" s="60">
         <v>3</v>
       </c>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="60">
+      <c r="L18" s="60">
         <v>2</v>
       </c>
-      <c r="K18" s="61"/>
-      <c r="L18" s="62">
+      <c r="M18" s="62">
         <v>1</v>
       </c>
-      <c r="M18" s="61"/>
       <c r="N18" s="61"/>
       <c r="O18" s="61"/>
       <c r="P18" s="61"/>
       <c r="Q18" s="61"/>
     </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="19" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="59" t="s">
         <v>56</v>
       </c>
@@ -12782,26 +12787,24 @@
       <c r="C19" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="61"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
       <c r="F19" s="60">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19" s="60">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19" s="60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I19" s="60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J19" s="60">
-        <v>7</v>
-      </c>
-      <c r="K19" s="60">
         <v>6</v>
       </c>
+      <c r="K19" s="61"/>
       <c r="L19" s="60">
         <v>5</v>
       </c>
@@ -12819,7 +12822,7 @@
       </c>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="20" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="59" t="s">
         <v>60</v>
       </c>
@@ -12829,30 +12832,24 @@
       <c r="C20" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="71">
-        <v>12</v>
-      </c>
-      <c r="E20" s="60">
-        <v>11</v>
-      </c>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
       <c r="F20" s="60">
         <v>10</v>
       </c>
       <c r="G20" s="60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I20" s="60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J20" s="60">
-        <v>6</v>
-      </c>
-      <c r="K20" s="60">
         <v>5</v>
       </c>
+      <c r="K20" s="61"/>
       <c r="L20" s="60">
         <v>4</v>
       </c>
@@ -12868,7 +12865,7 @@
       <c r="P20" s="61"/>
       <c r="Q20" s="61"/>
     </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="21" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="59" t="s">
         <v>62</v>
       </c>
@@ -12878,30 +12875,24 @@
       <c r="C21" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="71">
-        <v>12</v>
-      </c>
-      <c r="E21" s="60">
-        <v>11</v>
-      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
       <c r="F21" s="60">
         <v>10</v>
       </c>
       <c r="G21" s="60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H21" s="60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I21" s="60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J21" s="60">
-        <v>6</v>
-      </c>
-      <c r="K21" s="60">
         <v>5</v>
       </c>
+      <c r="K21" s="61"/>
       <c r="L21" s="60">
         <v>4</v>
       </c>
@@ -12917,7 +12908,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="22" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="59" t="s">
         <v>64</v>
       </c>
@@ -12927,30 +12918,24 @@
       <c r="C22" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="71">
-        <v>12</v>
-      </c>
-      <c r="E22" s="60">
-        <v>11</v>
-      </c>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
       <c r="F22" s="60">
         <v>10</v>
       </c>
       <c r="G22" s="60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H22" s="60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I22" s="60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="60">
-        <v>6</v>
-      </c>
-      <c r="K22" s="60">
         <v>5</v>
       </c>
+      <c r="K22" s="61"/>
       <c r="L22" s="60">
         <v>4</v>
       </c>
@@ -12966,7 +12951,7 @@
       <c r="P22" s="61"/>
       <c r="Q22" s="61"/>
     </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="23" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="59" t="s">
         <v>66</v>
       </c>
@@ -12976,29 +12961,29 @@
       <c r="C23" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="71">
-        <v>11</v>
+      <c r="D23" s="60">
+        <v>10</v>
       </c>
       <c r="E23" s="60">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" s="60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" s="60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I23" s="60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J23" s="60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K23" s="60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L23" s="60">
         <v>3</v>
@@ -13013,7 +12998,7 @@
       <c r="P23" s="61"/>
       <c r="Q23" s="61"/>
     </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="24" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="59" t="s">
         <v>69</v>
       </c>
@@ -13023,8 +13008,8 @@
       <c r="C24" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="72"/>
-      <c r="E24" s="61"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="72"/>
       <c r="F24" s="61"/>
       <c r="G24" s="61"/>
       <c r="H24" s="61"/>
@@ -13040,7 +13025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="25" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="59" t="s">
         <v>71</v>
       </c>
@@ -13050,8 +13035,8 @@
       <c r="C25" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="72"/>
-      <c r="E25" s="61"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="72"/>
       <c r="F25" s="61"/>
       <c r="G25" s="61"/>
       <c r="H25" s="61"/>
@@ -13067,7 +13052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" thickBot="1">
+    <row r="26" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="59" t="s">
         <v>73</v>
       </c>
@@ -13077,8 +13062,8 @@
       <c r="C26" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="72"/>
-      <c r="E26" s="61"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="72"/>
       <c r="F26" s="61"/>
       <c r="G26" s="61"/>
       <c r="H26" s="61"/>
@@ -13096,5 +13081,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>